--- a/assets/modele/KmPro-modele-frais-kilometriques-2026.xlsx
+++ b/assets/modele/KmPro-modele-frais-kilometriques-2026.xlsx
@@ -387,7 +387,8 @@
     </comment>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>Ligne d’exemple : effacez-la et saisissez vos trajets.</t>
+        <t>Année d’exemple, à remplacer par vos trajets.
+Les formules des totaux restent valables une fois les lignes effacées.</t>
       </text>
     </comment>
   </commentList>
@@ -917,15 +918,15 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNT('JAN 26'!D2:D41)</f>
+        <f>COUNT('JAN 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>'JAN 26'!D42</f>
+        <f>'JAN 26'!D26</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>'JAN 26'!F42</f>
+        <f>'JAN 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -936,15 +937,15 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNT('FÉV 26'!D2:D41)</f>
+        <f>COUNT('FÉV 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C5" s="9">
-        <f>'FÉV 26'!D42</f>
+        <f>'FÉV 26'!D26</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>'FÉV 26'!F42</f>
+        <f>'FÉV 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -955,15 +956,15 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNT('MAR 26'!D2:D41)</f>
+        <f>COUNT('MAR 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>'MAR 26'!D42</f>
+        <f>'MAR 26'!D26</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>'MAR 26'!F42</f>
+        <f>'MAR 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -974,15 +975,15 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNT('AVR 26'!D2:D41)</f>
+        <f>COUNT('AVR 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>'AVR 26'!D42</f>
+        <f>'AVR 26'!D26</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>'AVR 26'!F42</f>
+        <f>'AVR 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -993,15 +994,15 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNT('MAI 26'!D2:D41)</f>
+        <f>COUNT('MAI 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>'MAI 26'!D42</f>
+        <f>'MAI 26'!D26</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>'MAI 26'!F42</f>
+        <f>'MAI 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1012,15 +1013,15 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNT('JUIN 26'!D2:D41)</f>
+        <f>COUNT('JUIN 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>'JUIN 26'!D42</f>
+        <f>'JUIN 26'!D26</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>'JUIN 26'!F42</f>
+        <f>'JUIN 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1031,15 +1032,15 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <f>COUNT('JUIL 26'!D2:D41)</f>
+        <f>COUNT('JUIL 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>'JUIL 26'!D42</f>
+        <f>'JUIL 26'!D26</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>'JUIL 26'!F42</f>
+        <f>'JUIL 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1050,15 +1051,15 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <f>COUNT('AOÛ 26'!D2:D41)</f>
+        <f>COUNT('AOÛ 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>'AOÛ 26'!D42</f>
+        <f>'AOÛ 26'!D26</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>'AOÛ 26'!F42</f>
+        <f>'AOÛ 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1069,15 +1070,15 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>COUNT('SEP 26'!D2:D41)</f>
+        <f>COUNT('SEP 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>'SEP 26'!D42</f>
+        <f>'SEP 26'!D26</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>'SEP 26'!F42</f>
+        <f>'SEP 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1088,15 +1089,15 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>COUNT('OCT 26'!D2:D41)</f>
+        <f>COUNT('OCT 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>'OCT 26'!D42</f>
+        <f>'OCT 26'!D26</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>'OCT 26'!F42</f>
+        <f>'OCT 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1107,15 +1108,15 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNT('NOV 26'!D2:D41)</f>
+        <f>COUNT('NOV 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>'NOV 26'!D42</f>
+        <f>'NOV 26'!D26</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>'NOV 26'!F42</f>
+        <f>'NOV 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1126,15 +1127,15 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>COUNT('DÉC 26'!D2:D41)</f>
+        <f>COUNT('DÉC 26'!D2:D25)</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>'DÉC 26'!D42</f>
+        <f>'DÉC 26'!D26</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>'DÉC 26'!F42</f>
+        <f>'DÉC 26'!F26</f>
         <v/>
       </c>
     </row>
@@ -1172,7 +1173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1222,124 +1223,324 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Maison Favre – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Épagny AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>SCI Rivière – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Maison Favre – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Thonon-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Hôtel du Lac – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chamonix AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Sport Évasion – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Épagny AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>SCI Rivière – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cluses AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Clinique des Alpes – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -1510,215 +1711,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1732,7 +1741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1782,124 +1791,324 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Épagny AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>SCI Rivière – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Sallanches AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Chalets Dubois – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Megève AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Résidence Belvédère – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Épagny</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>SCI Rivière – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -2070,215 +2279,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2292,7 +2309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2342,136 +2359,356 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>04/11/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Les Gets AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Office de tourisme – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Bourg-en-Bresse AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>224</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Ain Logistique – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>16/11/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>23/11/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Les Gets AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Office de tourisme – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>25/11/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Aix-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Domaine Bertin – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>26/11/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F12" s="6">
         <f>IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -2630,215 +2867,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2852,7 +2897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2902,148 +2947,388 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Sallanches AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Chalets Dubois – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Maison Favre – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Rumilly AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Mairie de Rumilly – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Bourg-en-Bresse AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Ain Logistique – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Les Gets AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Office de tourisme – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>21/12/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Maison Favre – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>22/12/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Maison Favre – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>23/12/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Lyon AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Studio Rhône – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>24/12/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Thonon-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Hôtel du Lac – Devis sur place</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>29/12/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F12" s="6">
         <f>IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Maison Favre – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>30/12/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F13" s="10">
         <f>IF(D13="","",D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Maison Favre – Devis sur place</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n"/>
@@ -3190,215 +3475,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3412,7 +3505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3464,7 +3557,7 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3474,11 +3567,11 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Bureau &gt; Lyon AR</t>
+          <t>Bureau &gt; Chambéry AR</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>236</v>
+        <v>107</v>
       </c>
       <c r="E2" s="16" t="n">
         <v>0.357</v>
@@ -3489,153 +3582,393 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Atelier Morel – Rendez-vous client</t>
+          <t>Maison Favre – Livraison</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Épagny</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>SCI Rivière – Livraison</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Les Gets AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Office de tourisme – Livraison</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cluses AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Clinique des Alpes – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Grenoble AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>210</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Groupe Isère – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F12" s="6">
         <f>IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Épagny AR</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F13" s="10">
         <f>IF(D13="","",D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>SCI Rivière – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="16" t="n"/>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F14" s="6">
         <f>IF(D14="","",D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Livraison</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -3770,215 +4103,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3992,7 +4133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4042,160 +4183,420 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Bourg-en-Bresse AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>229</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Ain Logistique – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Rumilly</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Mairie de Rumilly – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Lyon AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>276</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Studio Rhône – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Bourg-en-Bresse AR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F12" s="6">
         <f>IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Ain Logistique – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Thonon-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>142</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F13" s="10">
         <f>IF(D13="","",D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Hôtel du Lac – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="16" t="n"/>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F14" s="6">
         <f>IF(D14="","",D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Maison Favre – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -4330,215 +4731,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4552,7 +4761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4602,124 +4811,324 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Rumilly AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Mairie de Rumilly – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Lyon AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Studio Rhône – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Sallanches AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Chalets Dubois – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -4890,215 +5299,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5112,7 +5329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5162,124 +5379,324 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Devis sur place</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Livraison</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Thonon-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Hôtel du Lac – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Devis sur place</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Maison Favre – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Megève AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Résidence Belvédère – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Maison Favre – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Aix-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Domaine Bertin – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -5450,215 +5867,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5672,7 +5897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5722,136 +5947,356 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Sallanches AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Chalets Dubois – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Devis sur place</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cluses AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Clinique des Alpes – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy AR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F12" s="6">
         <f>IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -6010,215 +6455,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6232,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6282,136 +6535,356 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Épagny</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>SCI Rivière – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Lyon AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>279</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Studio Rhône – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Livraison</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cluses AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Clinique des Alpes – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Repérage</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Thonon-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F12" s="6">
         <f>IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Hôtel du Lac – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -6570,215 +7043,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6792,7 +7073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6842,124 +7123,324 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Rumilly AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Mairie de Rumilly – Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Chambéry AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Maison Favre – Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Thonon-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Hôtel du Lac – Formation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Sallanches AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Chalets Dubois – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet AR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Thonon-les-Bains AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Hôtel du Lac – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Lyon AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>276</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Studio Rhône – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Meythet</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Menuiserie Goy – Livraison</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Rendez-vous client</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -7130,215 +7611,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7352,7 +7641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7402,148 +7691,388 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Grenoble AR</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F2" s="6">
         <f>IF(D2="","",D2*E2)</f>
         <v/>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Groupe Isère – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F3" s="10">
         <f>IF(D3="","",D3*E3)</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Tournage</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F4" s="6">
         <f>IF(D4="","",D4*E4)</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Annecy</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F5" s="10">
         <f>IF(D5="","",D5*E5)</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Atelier Morel – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F6" s="6">
         <f>IF(D6="","",D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Réunion de projet</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F7" s="10">
         <f>IF(D7="","",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Lyon AR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F8" s="6">
         <f>IF(D8="","",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Studio Rhône – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Sallanches AR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F9" s="10">
         <f>IF(D9="","",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Chalets Dubois – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Seynod AR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F10" s="6">
         <f>IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet Léger – Suivi de chantier</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; La Roche-sur-Foron AR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F11" s="10">
         <f>IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Alpes Usinage – Visite de site</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Rumilly AR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F12" s="6">
         <f>IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Mairie de Rumilly – Présentation du projet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Peugeot 3008</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Bureau &gt; Cran-Gevrier AR</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.357</v>
+      </c>
       <c r="F13" s="10">
         <f>IF(D13="","",D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Garage Pernet – Livraison</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n"/>
@@ -7690,215 +8219,23 @@
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="6">
-        <f>IF(D26="","",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="10">
-        <f>IF(D27="","",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="6">
-        <f>IF(D28="","",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="10">
-        <f>IF(D29="","",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="6">
-        <f>IF(D30="","",D30*E30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="10">
-        <f>IF(D31="","",D31*E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="6">
-        <f>IF(D32="","",D32*E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="10">
-        <f>IF(D33="","",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="6">
-        <f>IF(D34="","",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="10">
-        <f>IF(D35="","",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="6">
-        <f>IF(D36="","",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="10">
-        <f>IF(D37="","",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="6">
-        <f>IF(D38="","",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="10">
-        <f>IF(D39="","",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="6">
-        <f>IF(D40="","",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="10">
-        <f>IF(D41="","",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="13">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="13">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="14">
+        <f>SUM(F2:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
